--- a/Discussion/vocus01/視覺化阻塞原因.xlsx
+++ b/Discussion/vocus01/視覺化阻塞原因.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0d39fb11249e9e67/Documents/2026/NonBlockingLife/Discussion/vocus01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="8_{AED6DA2D-5B40-4A95-BF84-34E2CEE279CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{006DEDD3-3F71-41AB-8AE0-E337E674421B}"/>
+  <xr:revisionPtr revIDLastSave="82" documentId="8_{AED6DA2D-5B40-4A95-BF84-34E2CEE279CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49D065C2-39C2-443D-BBBE-F2F1747C5C8D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D2E8DEBD-0F2A-472C-BCB0-EAA166107B71}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{D2E8DEBD-0F2A-472C-BCB0-EAA166107B71}"/>
   </bookViews>
   <sheets>
     <sheet name="原本" sheetId="1" r:id="rId1"/>
     <sheet name="NBL" sheetId="3" r:id="rId2"/>
+    <sheet name="Projectile" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="2">
   <si>
     <t>x</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,6 +55,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -93,15 +97,25 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="176" formatCode="0.00_ "/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4125,6 +4139,2476 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-TW"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Projectile!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Projectile!$A$2:$A$200</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="199"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.04</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.06</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.08</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.1100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.1399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.17</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.19</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.28</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.29</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1.32</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1.33</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1.34</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1.36</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1.37</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.38</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.39</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.41</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.44</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.46</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.48</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Projectile!$B$2:$B$200</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="199"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9510000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19804000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29558999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39216000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.48775000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.58235999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.67599000000000009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.76863999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.86030999999999991</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.95099999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.04071</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.12944</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.21719</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.30396</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.38975</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4745600000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.5583900000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.6412399999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.7231099999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.8039999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.8839100000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9628400000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0407900000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.1177600000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1937500000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2687599999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3427899999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4158400000000002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.4879099999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.6291099999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.6982400000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.7663900000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.8335600000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.89975</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.9649599999999996</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.0291900000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.0924399999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.1547100000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.2159999999999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.2763099999999996</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.3356400000000002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.3939899999999996</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.4513600000000002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.5077499999999997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.5631600000000003</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.617589999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.6710399999999996</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.7235100000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.7749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.8255099999999995</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.8750400000000003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.9235900000000004</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.9711600000000002</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.0177499999999995</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.0633600000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4.1079899999999991</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4.1516399999999996</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.1943099999999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4.2359999999999998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4.2767099999999996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.3164400000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4.3551899999999995</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4.3929600000000004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.4297500000000003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.46556</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.5003899999999994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.5342400000000005</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.5671099999999996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.5990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.6299099999999989</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.6598399999999991</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4.68879</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.7167600000000007</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.7437500000000004</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.7697599999999998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.7947899999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4.8188399999999998</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4.8419099999999995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.863999999999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.885110000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.9052399999999992</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.9243899999999989</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.9425600000000003</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.9597499999999997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.9759599999999997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.9911899999999996</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.0054400000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.0187100000000004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.0309999999999988</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5.0423099999999987</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5.0526400000000002</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5.0619899999999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.0703599999999982</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.07775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.0841599999999998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.0895899999999994</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.0940400000000006</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.0975099999999998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.1015099999999993</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.1020399999999988</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.1015900000000007</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5.1001599999999998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.0977499999999996</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5.09436</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.0899900000000002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.0846399999999994</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.0783099999999992</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.0709999999999988</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5.06271</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.0534400000000002</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5.0431900000000001</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5.0319599999999989</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.0197500000000002</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.0065599999999995</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.9923899999999994</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.9772399999999992</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4.9611099999999988</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4.944</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4.9259099999999991</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4.906839999999999</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.8867900000000004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4.8657599999999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4.8437499999999991</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4.8207599999999982</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.7967899999999988</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4.7718399999999992</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4.7459099999999985</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4.7189999999999994</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4.6911100000000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.6622399999999988</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4.6323899999999991</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4.6015599999999974</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4.5697499999999991</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4.5369599999999988</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4.50319</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4.4684399999999993</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4.4327100000000002</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4.3960000000000008</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4.3583099999999995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4.3196399999999979</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4.2799899999999997</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4.2393599999999978</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4.1977499999999992</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4.1551600000000004</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4.1115899999999996</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4.0670400000000004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4.0215099999999993</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.9749999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4902-40FF-AB7A-4706ED6CFDDF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1362224047"/>
+        <c:axId val="1362223567"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1362224047"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1362223567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1362223567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1362224047"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-TW"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Projectile!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>y</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Projectile!$A$2:$A$152</c:f>
+              <c:numCache>
+                <c:formatCode>0.00_ </c:formatCode>
+                <c:ptCount val="151"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.11</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.17</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.21</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.22</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.23</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.27</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.28000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.28999999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.31</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.32</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.33</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.34</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.36</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.37</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.38</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.39</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.41</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.43</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.44</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.46</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.47</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.48</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.49</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.52</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.53</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.54</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.57999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.59</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.61</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.62</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.64</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.66</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.67</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.68</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.69</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.71</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.72</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.73</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.74</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.76</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.77</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.78</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.79</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.81</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.82</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.83</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.84</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.86</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.87</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.88</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.89</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.91</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.92</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.93</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.94</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.96</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.97</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.98</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.99</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.01</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.02</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.03</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.04</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.05</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.06</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.07</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.08</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.0900000000000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.1000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.1100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.1200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.1299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.1399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.1499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.17</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.18</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.19</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>1.2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.21</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>1.22</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>1.23</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>1.24</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1.26</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1.27</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>1.28</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1.29</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>1.3</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1.31</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>1.32</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1.33</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1.34</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1.35</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1.36</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1.37</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.38</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.39</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.4</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.41</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.42</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1.43</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>1.44</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.45</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1.46</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>1.47</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>1.48</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>1.49</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Projectile!$B$2:$B$152</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="151"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9510000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19804000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29558999999999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.39216000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.48775000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.58235999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.67599000000000009</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.76863999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.86030999999999991</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.95099999999999996</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.04071</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.12944</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.21719</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.30396</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.38975</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.4745600000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.5583900000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.6412399999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.7231099999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.8039999999999998</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.8839100000000002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9628400000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0407900000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.1177600000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1937500000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2687599999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3427899999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4158400000000002</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.4879099999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.5590000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.6291099999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.6982400000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.7663900000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.8335600000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.89975</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.9649599999999996</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.0291900000000003</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.0924399999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.1547100000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.2159999999999997</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.2763099999999996</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.3356400000000002</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.3939899999999996</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.4513600000000002</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.5077499999999997</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.5631600000000003</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.617589999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.6710399999999996</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.7235100000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.7749999999999999</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.8255099999999995</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.8750400000000003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.9235900000000004</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.9711600000000002</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.0177499999999995</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>4.0633600000000003</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>4.1079899999999991</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>4.1516399999999996</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.1943099999999998</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4.2359999999999998</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>4.2767099999999996</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>4.3164400000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>4.3551899999999995</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>4.3929600000000004</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.4297500000000003</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.46556</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.5003899999999994</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.5342400000000005</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.5671099999999996</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.5990000000000002</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.6299099999999989</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.6598399999999991</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>4.68879</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.7167600000000007</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.7437500000000004</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.7697599999999998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.7947899999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4.8188399999999998</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4.8419099999999995</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.863999999999999</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.885110000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.9052399999999992</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.9243899999999989</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.9425600000000003</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.9597499999999997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.9759599999999997</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.9911899999999996</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5.0054400000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5.0187100000000004</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5.0309999999999988</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5.0423099999999987</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5.0526400000000002</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5.0619899999999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.0703599999999982</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.07775</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.0841599999999998</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.0895899999999994</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.0940400000000006</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.0975099999999998</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.0999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5.1015099999999993</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5.1020399999999988</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5.1015900000000007</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5.1001599999999998</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5.0977499999999996</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5.09436</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5.0899900000000002</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5.0846399999999994</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5.0783099999999992</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>5.0709999999999988</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5.06271</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5.0534400000000002</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>5.0431900000000001</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5.0319599999999989</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5.0197500000000002</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5.0065599999999995</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.9923899999999994</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4.9772399999999992</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4.9611099999999988</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4.944</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4.9259099999999991</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4.906839999999999</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4.8867900000000004</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4.8657599999999999</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4.8437499999999991</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4.8207599999999982</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4.7967899999999988</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4.7718399999999992</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4.7459099999999985</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4.7189999999999994</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4.6911100000000001</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4.6622399999999988</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4.6323899999999991</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4.6015599999999974</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4.5697499999999991</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4.5369599999999988</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4.50319</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4.4684399999999993</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4.4327100000000002</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4.3960000000000008</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4.3583099999999995</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4.3196399999999979</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4.2799899999999997</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4.2393599999999978</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4.1977499999999992</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4.1551600000000004</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4.1115899999999996</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4.0670400000000004</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4.0215099999999993</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3.9749999999999996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9628-4DC9-9B88-1EFE351C3376}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="566358927"/>
+        <c:axId val="566358447"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="566358927"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>x</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="566358447"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="566358447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" altLang="zh-TW"/>
+                  <a:t>y</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-TW" altLang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-TW"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-TW"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="566358927"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-TW"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4166,6 +6650,86 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5205,6 +7769,1038 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="lt1"/>
     </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -6305,8 +9901,525 @@
 </c:userShapes>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>442912</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>190</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18E56757-9645-E345-2338-611EB6DFC969}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>142</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="圖表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6B0CE99-BA0D-E8A4-175C-65218979714C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>424974</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>59880</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1487587" cy="393762"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="文字方塊 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B9F6A75-33F8-99E3-A818-094838455741}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7282974" y="28349130"/>
+              <a:ext cx="1487587" cy="393762"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑥</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>0</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑣</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑥</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡</m:t>
+                    </m:r>
+                  </m:oMath>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑦</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>= </m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>0</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>+</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑣</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑦</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑡</m:t>
+                    </m:r>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>−</m:t>
+                    </m:r>
+                    <m:f>
+                      <m:fPr>
+                        <m:type m:val="skw"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:fPr>
+                      <m:num>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>1</m:t>
+                        </m:r>
+                      </m:num>
+                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:den>
+                    </m:f>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑔</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="4" name="文字方塊 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B9F6A75-33F8-99E3-A818-094838455741}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7282974" y="28349130"/>
+              <a:ext cx="1487587" cy="393762"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>0+𝑣</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥 𝑡</a:t>
+              </a:r>
+              <a:br>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0"/>
+              </a:br>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑦= 𝑦</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>0+𝑣</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑦 𝑡−1</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>⁄</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2 𝑔𝑡</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-TW" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2</a:t>
+              </a:r>
+              <a:endParaRPr lang="zh-TW" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B1C04B77-E2C2-4FEB-AF9D-93E4C3FA9D20}" name="表格1" displayName="表格1" ref="A1:B1048576" totalsRowShown="0">
+  <autoFilter ref="A1:B1048576" xr:uid="{B1C04B77-E2C2-4FEB-AF9D-93E4C3FA9D20}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{D5EC23D0-F7DE-44D2-9D50-563A6AB1CEBF}" name="x" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{617EB581-F86D-4FA2-A7F8-8C68B2CCC9C0}" name="y" dataDxfId="0">
+      <calculatedColumnFormula>10*A2-4.9*POWER(A2,2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12044,4 +16157,1389 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3383C7-2A28-4C50-87C0-65817CA32E2B}">
+  <dimension ref="A1:B152"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:B65" si="0">10*A2-4.9*POWER(A2,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <f t="shared" si="0"/>
+        <v>9.9510000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>0.19804000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>0.29558999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>0.39216000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>0.48775000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0.58235999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>0.67599000000000009</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="0"/>
+        <v>0.76863999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="0"/>
+        <v>0.86030999999999991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="0"/>
+        <v>0.95099999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="0"/>
+        <v>1.04071</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="0"/>
+        <v>1.12944</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="0"/>
+        <v>1.21719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>1.30396</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>1.38975</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>1.4745600000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>1.5583900000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>1.6412399999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>1.7231099999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>1.8039999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>1.8839100000000002</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>1.9628400000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>2.0407900000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>2.1177600000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>2.1937500000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>2.2687599999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>2.3427899999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>2.4158400000000002</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>2.4879099999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>2.5590000000000002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>2.6291099999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="0"/>
+        <v>2.6982400000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <f t="shared" si="0"/>
+        <v>2.7663900000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="0"/>
+        <v>2.8335600000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <f t="shared" si="0"/>
+        <v>2.89975</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="0"/>
+        <v>2.9649599999999996</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <f t="shared" si="0"/>
+        <v>3.0291900000000003</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="0"/>
+        <v>3.0924399999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <f t="shared" si="0"/>
+        <v>3.1547100000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="0"/>
+        <v>3.2159999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <f t="shared" si="0"/>
+        <v>3.2763099999999996</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="0"/>
+        <v>3.3356400000000002</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <f t="shared" si="0"/>
+        <v>3.3939899999999996</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="0"/>
+        <v>3.4513600000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <f t="shared" si="0"/>
+        <v>3.5077499999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="0"/>
+        <v>3.5631600000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <f t="shared" si="0"/>
+        <v>3.617589999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="0"/>
+        <v>3.6710399999999996</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <f t="shared" si="0"/>
+        <v>3.7235100000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="0"/>
+        <v>3.7749999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <f t="shared" si="0"/>
+        <v>3.8255099999999995</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="0"/>
+        <v>3.8750400000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <f t="shared" si="0"/>
+        <v>3.9235900000000004</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="0"/>
+        <v>3.9711600000000002</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="B57">
+        <f t="shared" si="0"/>
+        <v>4.0177499999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="0"/>
+        <v>4.0633600000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="B59">
+        <f t="shared" si="0"/>
+        <v>4.1079899999999991</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="0"/>
+        <v>4.1516399999999996</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <f t="shared" si="0"/>
+        <v>4.1943099999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="0"/>
+        <v>4.2359999999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <f t="shared" si="0"/>
+        <v>4.2767099999999996</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="0"/>
+        <v>4.3164400000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="0"/>
+        <v>4.3551899999999995</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <f t="shared" ref="B66:B129" si="1">10*A66-4.9*POWER(A66,2)</f>
+        <v>4.3929600000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <f t="shared" si="1"/>
+        <v>4.4297500000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="1"/>
+        <v>4.46556</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <f t="shared" si="1"/>
+        <v>4.5003899999999994</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="1"/>
+        <v>4.5342400000000005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="B71">
+        <f t="shared" si="1"/>
+        <v>4.5671099999999996</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="1"/>
+        <v>4.5990000000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <f t="shared" si="1"/>
+        <v>4.6299099999999989</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="1"/>
+        <v>4.6598399999999991</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <f t="shared" si="1"/>
+        <v>4.68879</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="1"/>
+        <v>4.7167600000000007</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <f t="shared" si="1"/>
+        <v>4.7437500000000004</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="1"/>
+        <v>4.7697599999999998</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <f t="shared" si="1"/>
+        <v>4.7947899999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="1"/>
+        <v>4.8188399999999998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <f t="shared" si="1"/>
+        <v>4.8419099999999995</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="1"/>
+        <v>4.863999999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="B83">
+        <f t="shared" si="1"/>
+        <v>4.885110000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="1"/>
+        <v>4.9052399999999992</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>0.83</v>
+      </c>
+      <c r="B85">
+        <f t="shared" si="1"/>
+        <v>4.9243899999999989</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="1"/>
+        <v>4.9425600000000003</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <f t="shared" si="1"/>
+        <v>4.9597499999999997</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <f t="shared" si="1"/>
+        <v>4.9759599999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <f t="shared" si="1"/>
+        <v>4.9911899999999996</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <f t="shared" si="1"/>
+        <v>5.0054400000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <f t="shared" si="1"/>
+        <v>5.0187100000000004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <f t="shared" si="1"/>
+        <v>5.0309999999999988</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <f t="shared" si="1"/>
+        <v>5.0423099999999987</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <f t="shared" si="1"/>
+        <v>5.0526400000000002</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <f t="shared" si="1"/>
+        <v>5.0619899999999998</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="B96">
+        <f t="shared" si="1"/>
+        <v>5.0703599999999982</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="B97">
+        <f t="shared" si="1"/>
+        <v>5.07775</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <f t="shared" si="1"/>
+        <v>5.0841599999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <f t="shared" si="1"/>
+        <v>5.0895899999999994</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <f t="shared" si="1"/>
+        <v>5.0940400000000006</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <f t="shared" si="1"/>
+        <v>5.0975099999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>1</v>
+      </c>
+      <c r="B102">
+        <f t="shared" si="1"/>
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>1.01</v>
+      </c>
+      <c r="B103">
+        <f t="shared" si="1"/>
+        <v>5.1015099999999993</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>1.02</v>
+      </c>
+      <c r="B104">
+        <f t="shared" si="1"/>
+        <v>5.1020399999999988</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>1.03</v>
+      </c>
+      <c r="B105">
+        <f t="shared" si="1"/>
+        <v>5.1015900000000007</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>1.04</v>
+      </c>
+      <c r="B106">
+        <f t="shared" si="1"/>
+        <v>5.1001599999999998</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>1.05</v>
+      </c>
+      <c r="B107">
+        <f t="shared" si="1"/>
+        <v>5.0977499999999996</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>1.06</v>
+      </c>
+      <c r="B108">
+        <f t="shared" si="1"/>
+        <v>5.09436</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>1.07</v>
+      </c>
+      <c r="B109">
+        <f t="shared" si="1"/>
+        <v>5.0899900000000002</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>1.08</v>
+      </c>
+      <c r="B110">
+        <f t="shared" si="1"/>
+        <v>5.0846399999999994</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="B111">
+        <f t="shared" si="1"/>
+        <v>5.0783099999999992</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B112">
+        <f t="shared" si="1"/>
+        <v>5.0709999999999988</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="B113">
+        <f t="shared" si="1"/>
+        <v>5.06271</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="B114">
+        <f t="shared" si="1"/>
+        <v>5.0534400000000002</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="B115">
+        <f t="shared" si="1"/>
+        <v>5.0431900000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="B116">
+        <f t="shared" si="1"/>
+        <v>5.0319599999999989</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="B117">
+        <f t="shared" si="1"/>
+        <v>5.0197500000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="B118">
+        <f t="shared" si="1"/>
+        <v>5.0065599999999995</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>1.17</v>
+      </c>
+      <c r="B119">
+        <f t="shared" si="1"/>
+        <v>4.9923899999999994</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>1.18</v>
+      </c>
+      <c r="B120">
+        <f t="shared" si="1"/>
+        <v>4.9772399999999992</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>1.19</v>
+      </c>
+      <c r="B121">
+        <f t="shared" si="1"/>
+        <v>4.9611099999999988</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="B122">
+        <f t="shared" si="1"/>
+        <v>4.944</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>1.21</v>
+      </c>
+      <c r="B123">
+        <f t="shared" si="1"/>
+        <v>4.9259099999999991</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>1.22</v>
+      </c>
+      <c r="B124">
+        <f t="shared" si="1"/>
+        <v>4.906839999999999</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>1.23</v>
+      </c>
+      <c r="B125">
+        <f t="shared" si="1"/>
+        <v>4.8867900000000004</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>1.24</v>
+      </c>
+      <c r="B126">
+        <f t="shared" si="1"/>
+        <v>4.8657599999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>1.25</v>
+      </c>
+      <c r="B127">
+        <f t="shared" si="1"/>
+        <v>4.8437499999999991</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>1.26</v>
+      </c>
+      <c r="B128">
+        <f t="shared" si="1"/>
+        <v>4.8207599999999982</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="B129">
+        <f t="shared" si="1"/>
+        <v>4.7967899999999988</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>1.28</v>
+      </c>
+      <c r="B130">
+        <f t="shared" ref="B130:B193" si="2">10*A130-4.9*POWER(A130,2)</f>
+        <v>4.7718399999999992</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>1.29</v>
+      </c>
+      <c r="B131">
+        <f t="shared" si="2"/>
+        <v>4.7459099999999985</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="B132">
+        <f t="shared" si="2"/>
+        <v>4.7189999999999994</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>1.31</v>
+      </c>
+      <c r="B133">
+        <f t="shared" si="2"/>
+        <v>4.6911100000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="B134">
+        <f t="shared" si="2"/>
+        <v>4.6622399999999988</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>1.33</v>
+      </c>
+      <c r="B135">
+        <f t="shared" si="2"/>
+        <v>4.6323899999999991</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>1.34</v>
+      </c>
+      <c r="B136">
+        <f t="shared" si="2"/>
+        <v>4.6015599999999974</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="B137">
+        <f t="shared" si="2"/>
+        <v>4.5697499999999991</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>1.36</v>
+      </c>
+      <c r="B138">
+        <f t="shared" si="2"/>
+        <v>4.5369599999999988</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>1.37</v>
+      </c>
+      <c r="B139">
+        <f t="shared" si="2"/>
+        <v>4.50319</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>1.38</v>
+      </c>
+      <c r="B140">
+        <f t="shared" si="2"/>
+        <v>4.4684399999999993</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>1.39</v>
+      </c>
+      <c r="B141">
+        <f t="shared" si="2"/>
+        <v>4.4327100000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>1.4</v>
+      </c>
+      <c r="B142">
+        <f t="shared" si="2"/>
+        <v>4.3960000000000008</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>1.41</v>
+      </c>
+      <c r="B143">
+        <f t="shared" si="2"/>
+        <v>4.3583099999999995</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>1.42</v>
+      </c>
+      <c r="B144">
+        <f t="shared" si="2"/>
+        <v>4.3196399999999979</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>1.43</v>
+      </c>
+      <c r="B145">
+        <f t="shared" si="2"/>
+        <v>4.2799899999999997</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="B146">
+        <f t="shared" si="2"/>
+        <v>4.2393599999999978</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="B147">
+        <f t="shared" si="2"/>
+        <v>4.1977499999999992</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="B148">
+        <f t="shared" si="2"/>
+        <v>4.1551600000000004</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="B149">
+        <f t="shared" si="2"/>
+        <v>4.1115899999999996</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="B150">
+        <f t="shared" si="2"/>
+        <v>4.0670400000000004</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="B151">
+        <f t="shared" si="2"/>
+        <v>4.0215099999999993</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="B152">
+        <f t="shared" si="2"/>
+        <v>3.9749999999999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>